--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="44">
   <si>
     <t>name</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>cannon-mon</t>
+  </si>
+  <si>
+    <t>longLaser</t>
+  </si>
+  <si>
+    <t>锁定一个敌人发射持续的光束,光束每cd的时间造成一次伤害,光束持续命中的时间越长,伤害越高,在para1的时间里逐渐增长到最大para2的伤害(最大伤害为dmg*para2)</t>
+  </si>
+  <si>
+    <t>锁定一个敌人发射持续的光束,光束每cd的时间造成一次伤害,光束持续命中的时间越长,伤害越高,在para1的时间里逐渐增长到最大para2的伤害(最大伤害为dmg*para2),切换目标后伤害增加重置</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1092,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N506"/>
+  <dimension ref="A1:N606"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -19503,6 +19512,3803 @@
         <v>20</v>
       </c>
     </row>
+    <row r="507" spans="1:13">
+      <c r="A507" t="s">
+        <v>41</v>
+      </c>
+      <c r="B507" t="s">
+        <v>42</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+      <c r="D507">
+        <v>1</v>
+      </c>
+      <c r="E507">
+        <v>20</v>
+      </c>
+      <c r="F507">
+        <v>0.2</v>
+      </c>
+      <c r="G507">
+        <v>5</v>
+      </c>
+      <c r="H507">
+        <v>1</v>
+      </c>
+      <c r="I507">
+        <v>50</v>
+      </c>
+      <c r="L507">
+        <v>2</v>
+      </c>
+      <c r="M507">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="508" customFormat="1" spans="1:13">
+      <c r="A508" t="s">
+        <v>41</v>
+      </c>
+      <c r="B508" t="s">
+        <v>43</v>
+      </c>
+      <c r="C508">
+        <f t="shared" ref="C508:C571" si="54">C507+1</f>
+        <v>2</v>
+      </c>
+      <c r="D508">
+        <v>1</v>
+      </c>
+      <c r="E508">
+        <f t="shared" ref="E508:E571" si="55">ROUND(E507*1.2/5,IF(-(LEN(INT(ABS(E507*1.2/5)))-2)&lt;0,-(LEN(INT(ABS(E507*1.2/5)))-2),0))*5</f>
+        <v>25</v>
+      </c>
+      <c r="F508">
+        <v>0.2</v>
+      </c>
+      <c r="G508">
+        <v>5</v>
+      </c>
+      <c r="H508">
+        <v>1</v>
+      </c>
+      <c r="I508">
+        <f t="shared" ref="I508:I571" si="56">ROUND(I507*1.2/5,IF(-(LEN(INT(ABS(I507*1.2/5)))-2)&lt;0,-(LEN(INT(ABS(I507*1.2/5)))-2),0))*5</f>
+        <v>60</v>
+      </c>
+      <c r="L508">
+        <v>2</v>
+      </c>
+      <c r="M508">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="509" customFormat="1" spans="1:13">
+      <c r="A509" t="s">
+        <v>41</v>
+      </c>
+      <c r="B509" t="s">
+        <v>43</v>
+      </c>
+      <c r="C509">
+        <f t="shared" si="54"/>
+        <v>3</v>
+      </c>
+      <c r="D509">
+        <v>1</v>
+      </c>
+      <c r="E509">
+        <f t="shared" si="55"/>
+        <v>30</v>
+      </c>
+      <c r="F509">
+        <v>0.2</v>
+      </c>
+      <c r="G509">
+        <v>5</v>
+      </c>
+      <c r="H509">
+        <v>1</v>
+      </c>
+      <c r="I509">
+        <f t="shared" si="56"/>
+        <v>70</v>
+      </c>
+      <c r="L509">
+        <v>2</v>
+      </c>
+      <c r="M509">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="510" customFormat="1" spans="1:13">
+      <c r="A510" t="s">
+        <v>41</v>
+      </c>
+      <c r="B510" t="s">
+        <v>43</v>
+      </c>
+      <c r="C510">
+        <f t="shared" si="54"/>
+        <v>4</v>
+      </c>
+      <c r="D510">
+        <v>1</v>
+      </c>
+      <c r="E510">
+        <f t="shared" si="55"/>
+        <v>35</v>
+      </c>
+      <c r="F510">
+        <v>0.2</v>
+      </c>
+      <c r="G510">
+        <v>5</v>
+      </c>
+      <c r="H510">
+        <v>1</v>
+      </c>
+      <c r="I510">
+        <f t="shared" si="56"/>
+        <v>85</v>
+      </c>
+      <c r="L510">
+        <v>2</v>
+      </c>
+      <c r="M510">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="511" customFormat="1" spans="1:13">
+      <c r="A511" t="s">
+        <v>41</v>
+      </c>
+      <c r="B511" t="s">
+        <v>43</v>
+      </c>
+      <c r="C511">
+        <f t="shared" si="54"/>
+        <v>5</v>
+      </c>
+      <c r="D511">
+        <v>1</v>
+      </c>
+      <c r="E511">
+        <f t="shared" si="55"/>
+        <v>40</v>
+      </c>
+      <c r="F511">
+        <v>0.2</v>
+      </c>
+      <c r="G511">
+        <v>5</v>
+      </c>
+      <c r="H511">
+        <v>1</v>
+      </c>
+      <c r="I511">
+        <f t="shared" si="56"/>
+        <v>100</v>
+      </c>
+      <c r="L511">
+        <v>2</v>
+      </c>
+      <c r="M511">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="512" customFormat="1" spans="1:13">
+      <c r="A512" t="s">
+        <v>41</v>
+      </c>
+      <c r="B512" t="s">
+        <v>43</v>
+      </c>
+      <c r="C512">
+        <f t="shared" si="54"/>
+        <v>6</v>
+      </c>
+      <c r="D512">
+        <v>1</v>
+      </c>
+      <c r="E512">
+        <f t="shared" si="55"/>
+        <v>50</v>
+      </c>
+      <c r="F512">
+        <v>0.2</v>
+      </c>
+      <c r="G512">
+        <v>5</v>
+      </c>
+      <c r="H512">
+        <v>1</v>
+      </c>
+      <c r="I512">
+        <f t="shared" si="56"/>
+        <v>120</v>
+      </c>
+      <c r="L512">
+        <v>2</v>
+      </c>
+      <c r="M512">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="513" customFormat="1" spans="1:13">
+      <c r="A513" t="s">
+        <v>41</v>
+      </c>
+      <c r="B513" t="s">
+        <v>43</v>
+      </c>
+      <c r="C513">
+        <f t="shared" si="54"/>
+        <v>7</v>
+      </c>
+      <c r="D513">
+        <v>1</v>
+      </c>
+      <c r="E513">
+        <f t="shared" si="55"/>
+        <v>60</v>
+      </c>
+      <c r="F513">
+        <v>0.2</v>
+      </c>
+      <c r="G513">
+        <v>5</v>
+      </c>
+      <c r="H513">
+        <v>1</v>
+      </c>
+      <c r="I513">
+        <f t="shared" si="56"/>
+        <v>145</v>
+      </c>
+      <c r="L513">
+        <v>2</v>
+      </c>
+      <c r="M513">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="514" customFormat="1" spans="1:13">
+      <c r="A514" t="s">
+        <v>41</v>
+      </c>
+      <c r="B514" t="s">
+        <v>43</v>
+      </c>
+      <c r="C514">
+        <f t="shared" si="54"/>
+        <v>8</v>
+      </c>
+      <c r="D514">
+        <v>1</v>
+      </c>
+      <c r="E514">
+        <f t="shared" si="55"/>
+        <v>70</v>
+      </c>
+      <c r="F514">
+        <v>0.2</v>
+      </c>
+      <c r="G514">
+        <v>5</v>
+      </c>
+      <c r="H514">
+        <v>1</v>
+      </c>
+      <c r="I514">
+        <f t="shared" si="56"/>
+        <v>175</v>
+      </c>
+      <c r="L514">
+        <v>2</v>
+      </c>
+      <c r="M514">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="515" customFormat="1" spans="1:13">
+      <c r="A515" t="s">
+        <v>41</v>
+      </c>
+      <c r="B515" t="s">
+        <v>43</v>
+      </c>
+      <c r="C515">
+        <f t="shared" si="54"/>
+        <v>9</v>
+      </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
+      <c r="E515">
+        <f t="shared" si="55"/>
+        <v>85</v>
+      </c>
+      <c r="F515">
+        <v>0.2</v>
+      </c>
+      <c r="G515">
+        <v>5</v>
+      </c>
+      <c r="H515">
+        <v>1</v>
+      </c>
+      <c r="I515">
+        <f t="shared" si="56"/>
+        <v>210</v>
+      </c>
+      <c r="L515">
+        <v>2</v>
+      </c>
+      <c r="M515">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="516" customFormat="1" spans="1:13">
+      <c r="A516" t="s">
+        <v>41</v>
+      </c>
+      <c r="B516" t="s">
+        <v>43</v>
+      </c>
+      <c r="C516">
+        <f t="shared" si="54"/>
+        <v>10</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516">
+        <f t="shared" si="55"/>
+        <v>100</v>
+      </c>
+      <c r="F516">
+        <v>0.2</v>
+      </c>
+      <c r="G516">
+        <v>5</v>
+      </c>
+      <c r="H516">
+        <v>1</v>
+      </c>
+      <c r="I516">
+        <f t="shared" si="56"/>
+        <v>250</v>
+      </c>
+      <c r="L516">
+        <v>2</v>
+      </c>
+      <c r="M516">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="517" customFormat="1" spans="1:13">
+      <c r="A517" t="s">
+        <v>41</v>
+      </c>
+      <c r="B517" t="s">
+        <v>43</v>
+      </c>
+      <c r="C517">
+        <f t="shared" si="54"/>
+        <v>11</v>
+      </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
+      <c r="E517">
+        <f t="shared" si="55"/>
+        <v>120</v>
+      </c>
+      <c r="F517">
+        <v>0.2</v>
+      </c>
+      <c r="G517">
+        <v>5</v>
+      </c>
+      <c r="H517">
+        <v>1</v>
+      </c>
+      <c r="I517">
+        <f t="shared" si="56"/>
+        <v>300</v>
+      </c>
+      <c r="L517">
+        <v>2</v>
+      </c>
+      <c r="M517">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="518" customFormat="1" spans="1:13">
+      <c r="A518" t="s">
+        <v>41</v>
+      </c>
+      <c r="B518" t="s">
+        <v>43</v>
+      </c>
+      <c r="C518">
+        <f t="shared" si="54"/>
+        <v>12</v>
+      </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
+      <c r="E518">
+        <f t="shared" si="55"/>
+        <v>145</v>
+      </c>
+      <c r="F518">
+        <v>0.2</v>
+      </c>
+      <c r="G518">
+        <v>5</v>
+      </c>
+      <c r="H518">
+        <v>1</v>
+      </c>
+      <c r="I518">
+        <f t="shared" si="56"/>
+        <v>360</v>
+      </c>
+      <c r="L518">
+        <v>2</v>
+      </c>
+      <c r="M518">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13">
+      <c r="A519" t="s">
+        <v>41</v>
+      </c>
+      <c r="B519" t="s">
+        <v>43</v>
+      </c>
+      <c r="C519">
+        <f t="shared" si="54"/>
+        <v>13</v>
+      </c>
+      <c r="D519">
+        <v>1</v>
+      </c>
+      <c r="E519">
+        <f t="shared" si="55"/>
+        <v>175</v>
+      </c>
+      <c r="F519">
+        <v>0.2</v>
+      </c>
+      <c r="G519">
+        <v>5</v>
+      </c>
+      <c r="H519">
+        <v>1</v>
+      </c>
+      <c r="I519">
+        <f t="shared" si="56"/>
+        <v>430</v>
+      </c>
+      <c r="L519">
+        <v>2</v>
+      </c>
+      <c r="M519">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13">
+      <c r="A520" t="s">
+        <v>41</v>
+      </c>
+      <c r="B520" t="s">
+        <v>43</v>
+      </c>
+      <c r="C520">
+        <f t="shared" si="54"/>
+        <v>14</v>
+      </c>
+      <c r="D520">
+        <v>1</v>
+      </c>
+      <c r="E520">
+        <f t="shared" si="55"/>
+        <v>210</v>
+      </c>
+      <c r="F520">
+        <v>0.2</v>
+      </c>
+      <c r="G520">
+        <v>5</v>
+      </c>
+      <c r="H520">
+        <v>1</v>
+      </c>
+      <c r="I520">
+        <f t="shared" si="56"/>
+        <v>500</v>
+      </c>
+      <c r="L520">
+        <v>2</v>
+      </c>
+      <c r="M520">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13">
+      <c r="A521" t="s">
+        <v>41</v>
+      </c>
+      <c r="B521" t="s">
+        <v>43</v>
+      </c>
+      <c r="C521">
+        <f t="shared" si="54"/>
+        <v>15</v>
+      </c>
+      <c r="D521">
+        <v>1</v>
+      </c>
+      <c r="E521">
+        <f t="shared" si="55"/>
+        <v>250</v>
+      </c>
+      <c r="F521">
+        <v>0.2</v>
+      </c>
+      <c r="G521">
+        <v>5</v>
+      </c>
+      <c r="H521">
+        <v>1</v>
+      </c>
+      <c r="I521">
+        <f t="shared" si="56"/>
+        <v>600</v>
+      </c>
+      <c r="L521">
+        <v>2</v>
+      </c>
+      <c r="M521">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="522" spans="1:13">
+      <c r="A522" t="s">
+        <v>41</v>
+      </c>
+      <c r="B522" t="s">
+        <v>43</v>
+      </c>
+      <c r="C522">
+        <f t="shared" si="54"/>
+        <v>16</v>
+      </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
+      <c r="E522">
+        <f t="shared" si="55"/>
+        <v>300</v>
+      </c>
+      <c r="F522">
+        <v>0.2</v>
+      </c>
+      <c r="G522">
+        <v>5</v>
+      </c>
+      <c r="H522">
+        <v>1</v>
+      </c>
+      <c r="I522">
+        <f t="shared" si="56"/>
+        <v>700</v>
+      </c>
+      <c r="L522">
+        <v>2</v>
+      </c>
+      <c r="M522">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13">
+      <c r="A523" t="s">
+        <v>41</v>
+      </c>
+      <c r="B523" t="s">
+        <v>43</v>
+      </c>
+      <c r="C523">
+        <f t="shared" si="54"/>
+        <v>17</v>
+      </c>
+      <c r="D523">
+        <v>1</v>
+      </c>
+      <c r="E523">
+        <f t="shared" si="55"/>
+        <v>360</v>
+      </c>
+      <c r="F523">
+        <v>0.2</v>
+      </c>
+      <c r="G523">
+        <v>5</v>
+      </c>
+      <c r="H523">
+        <v>1</v>
+      </c>
+      <c r="I523">
+        <f t="shared" si="56"/>
+        <v>850</v>
+      </c>
+      <c r="L523">
+        <v>2</v>
+      </c>
+      <c r="M523">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13">
+      <c r="A524" t="s">
+        <v>41</v>
+      </c>
+      <c r="B524" t="s">
+        <v>43</v>
+      </c>
+      <c r="C524">
+        <f t="shared" si="54"/>
+        <v>18</v>
+      </c>
+      <c r="D524">
+        <v>1</v>
+      </c>
+      <c r="E524">
+        <f t="shared" si="55"/>
+        <v>430</v>
+      </c>
+      <c r="F524">
+        <v>0.2</v>
+      </c>
+      <c r="G524">
+        <v>5</v>
+      </c>
+      <c r="H524">
+        <v>1</v>
+      </c>
+      <c r="I524">
+        <f t="shared" si="56"/>
+        <v>1000</v>
+      </c>
+      <c r="L524">
+        <v>2</v>
+      </c>
+      <c r="M524">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13">
+      <c r="A525" t="s">
+        <v>41</v>
+      </c>
+      <c r="B525" t="s">
+        <v>43</v>
+      </c>
+      <c r="C525">
+        <f t="shared" si="54"/>
+        <v>19</v>
+      </c>
+      <c r="D525">
+        <v>1</v>
+      </c>
+      <c r="E525">
+        <f t="shared" si="55"/>
+        <v>500</v>
+      </c>
+      <c r="F525">
+        <v>0.2</v>
+      </c>
+      <c r="G525">
+        <v>5</v>
+      </c>
+      <c r="H525">
+        <v>1</v>
+      </c>
+      <c r="I525">
+        <f t="shared" si="56"/>
+        <v>1200</v>
+      </c>
+      <c r="L525">
+        <v>2</v>
+      </c>
+      <c r="M525">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13">
+      <c r="A526" t="s">
+        <v>41</v>
+      </c>
+      <c r="B526" t="s">
+        <v>43</v>
+      </c>
+      <c r="C526">
+        <f t="shared" si="54"/>
+        <v>20</v>
+      </c>
+      <c r="D526">
+        <v>1</v>
+      </c>
+      <c r="E526">
+        <f t="shared" si="55"/>
+        <v>600</v>
+      </c>
+      <c r="F526">
+        <v>0.2</v>
+      </c>
+      <c r="G526">
+        <v>5</v>
+      </c>
+      <c r="H526">
+        <v>1</v>
+      </c>
+      <c r="I526">
+        <f t="shared" si="56"/>
+        <v>1450</v>
+      </c>
+      <c r="L526">
+        <v>2</v>
+      </c>
+      <c r="M526">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13">
+      <c r="A527" t="s">
+        <v>41</v>
+      </c>
+      <c r="B527" t="s">
+        <v>43</v>
+      </c>
+      <c r="C527">
+        <f t="shared" si="54"/>
+        <v>21</v>
+      </c>
+      <c r="D527">
+        <v>1</v>
+      </c>
+      <c r="E527">
+        <f t="shared" si="55"/>
+        <v>700</v>
+      </c>
+      <c r="F527">
+        <v>0.2</v>
+      </c>
+      <c r="G527">
+        <v>5</v>
+      </c>
+      <c r="H527">
+        <v>1</v>
+      </c>
+      <c r="I527">
+        <f t="shared" si="56"/>
+        <v>1750</v>
+      </c>
+      <c r="L527">
+        <v>2</v>
+      </c>
+      <c r="M527">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13">
+      <c r="A528" t="s">
+        <v>41</v>
+      </c>
+      <c r="B528" t="s">
+        <v>43</v>
+      </c>
+      <c r="C528">
+        <f t="shared" si="54"/>
+        <v>22</v>
+      </c>
+      <c r="D528">
+        <v>1</v>
+      </c>
+      <c r="E528">
+        <f t="shared" si="55"/>
+        <v>850</v>
+      </c>
+      <c r="F528">
+        <v>0.2</v>
+      </c>
+      <c r="G528">
+        <v>5</v>
+      </c>
+      <c r="H528">
+        <v>1</v>
+      </c>
+      <c r="I528">
+        <f t="shared" si="56"/>
+        <v>2100</v>
+      </c>
+      <c r="L528">
+        <v>2</v>
+      </c>
+      <c r="M528">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13">
+      <c r="A529" t="s">
+        <v>41</v>
+      </c>
+      <c r="B529" t="s">
+        <v>43</v>
+      </c>
+      <c r="C529">
+        <f t="shared" si="54"/>
+        <v>23</v>
+      </c>
+      <c r="D529">
+        <v>1</v>
+      </c>
+      <c r="E529">
+        <f t="shared" si="55"/>
+        <v>1000</v>
+      </c>
+      <c r="F529">
+        <v>0.2</v>
+      </c>
+      <c r="G529">
+        <v>5</v>
+      </c>
+      <c r="H529">
+        <v>1</v>
+      </c>
+      <c r="I529">
+        <f t="shared" si="56"/>
+        <v>2500</v>
+      </c>
+      <c r="L529">
+        <v>2</v>
+      </c>
+      <c r="M529">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13">
+      <c r="A530" t="s">
+        <v>41</v>
+      </c>
+      <c r="B530" t="s">
+        <v>43</v>
+      </c>
+      <c r="C530">
+        <f t="shared" si="54"/>
+        <v>24</v>
+      </c>
+      <c r="D530">
+        <v>1</v>
+      </c>
+      <c r="E530">
+        <f t="shared" si="55"/>
+        <v>1200</v>
+      </c>
+      <c r="F530">
+        <v>0.2</v>
+      </c>
+      <c r="G530">
+        <v>5</v>
+      </c>
+      <c r="H530">
+        <v>1</v>
+      </c>
+      <c r="I530">
+        <f t="shared" si="56"/>
+        <v>3000</v>
+      </c>
+      <c r="L530">
+        <v>2</v>
+      </c>
+      <c r="M530">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13">
+      <c r="A531" t="s">
+        <v>41</v>
+      </c>
+      <c r="B531" t="s">
+        <v>43</v>
+      </c>
+      <c r="C531">
+        <f t="shared" si="54"/>
+        <v>25</v>
+      </c>
+      <c r="D531">
+        <v>1</v>
+      </c>
+      <c r="E531">
+        <f t="shared" si="55"/>
+        <v>1450</v>
+      </c>
+      <c r="F531">
+        <v>0.2</v>
+      </c>
+      <c r="G531">
+        <v>5</v>
+      </c>
+      <c r="H531">
+        <v>1</v>
+      </c>
+      <c r="I531">
+        <f t="shared" si="56"/>
+        <v>3600</v>
+      </c>
+      <c r="L531">
+        <v>2</v>
+      </c>
+      <c r="M531">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13">
+      <c r="A532" t="s">
+        <v>41</v>
+      </c>
+      <c r="B532" t="s">
+        <v>43</v>
+      </c>
+      <c r="C532">
+        <f t="shared" si="54"/>
+        <v>26</v>
+      </c>
+      <c r="D532">
+        <v>1</v>
+      </c>
+      <c r="E532">
+        <f t="shared" si="55"/>
+        <v>1750</v>
+      </c>
+      <c r="F532">
+        <v>0.2</v>
+      </c>
+      <c r="G532">
+        <v>5</v>
+      </c>
+      <c r="H532">
+        <v>1</v>
+      </c>
+      <c r="I532">
+        <f t="shared" si="56"/>
+        <v>4300</v>
+      </c>
+      <c r="L532">
+        <v>2</v>
+      </c>
+      <c r="M532">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13">
+      <c r="A533" t="s">
+        <v>41</v>
+      </c>
+      <c r="B533" t="s">
+        <v>43</v>
+      </c>
+      <c r="C533">
+        <f t="shared" si="54"/>
+        <v>27</v>
+      </c>
+      <c r="D533">
+        <v>1</v>
+      </c>
+      <c r="E533">
+        <f t="shared" si="55"/>
+        <v>2100</v>
+      </c>
+      <c r="F533">
+        <v>0.2</v>
+      </c>
+      <c r="G533">
+        <v>5</v>
+      </c>
+      <c r="H533">
+        <v>1</v>
+      </c>
+      <c r="I533">
+        <f t="shared" si="56"/>
+        <v>5000</v>
+      </c>
+      <c r="L533">
+        <v>2</v>
+      </c>
+      <c r="M533">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13">
+      <c r="A534" t="s">
+        <v>41</v>
+      </c>
+      <c r="B534" t="s">
+        <v>43</v>
+      </c>
+      <c r="C534">
+        <f t="shared" si="54"/>
+        <v>28</v>
+      </c>
+      <c r="D534">
+        <v>1</v>
+      </c>
+      <c r="E534">
+        <f t="shared" si="55"/>
+        <v>2500</v>
+      </c>
+      <c r="F534">
+        <v>0.2</v>
+      </c>
+      <c r="G534">
+        <v>5</v>
+      </c>
+      <c r="H534">
+        <v>1</v>
+      </c>
+      <c r="I534">
+        <f t="shared" si="56"/>
+        <v>6000</v>
+      </c>
+      <c r="L534">
+        <v>2</v>
+      </c>
+      <c r="M534">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13">
+      <c r="A535" t="s">
+        <v>41</v>
+      </c>
+      <c r="B535" t="s">
+        <v>43</v>
+      </c>
+      <c r="C535">
+        <f t="shared" si="54"/>
+        <v>29</v>
+      </c>
+      <c r="D535">
+        <v>1</v>
+      </c>
+      <c r="E535">
+        <f t="shared" si="55"/>
+        <v>3000</v>
+      </c>
+      <c r="F535">
+        <v>0.2</v>
+      </c>
+      <c r="G535">
+        <v>5</v>
+      </c>
+      <c r="H535">
+        <v>1</v>
+      </c>
+      <c r="I535">
+        <f t="shared" si="56"/>
+        <v>7000</v>
+      </c>
+      <c r="L535">
+        <v>2</v>
+      </c>
+      <c r="M535">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13">
+      <c r="A536" t="s">
+        <v>41</v>
+      </c>
+      <c r="B536" t="s">
+        <v>43</v>
+      </c>
+      <c r="C536">
+        <f t="shared" si="54"/>
+        <v>30</v>
+      </c>
+      <c r="D536">
+        <v>1</v>
+      </c>
+      <c r="E536">
+        <f t="shared" si="55"/>
+        <v>3600</v>
+      </c>
+      <c r="F536">
+        <v>0.2</v>
+      </c>
+      <c r="G536">
+        <v>5</v>
+      </c>
+      <c r="H536">
+        <v>1</v>
+      </c>
+      <c r="I536">
+        <f t="shared" si="56"/>
+        <v>8500</v>
+      </c>
+      <c r="L536">
+        <v>2</v>
+      </c>
+      <c r="M536">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13">
+      <c r="A537" t="s">
+        <v>41</v>
+      </c>
+      <c r="B537" t="s">
+        <v>43</v>
+      </c>
+      <c r="C537">
+        <f t="shared" si="54"/>
+        <v>31</v>
+      </c>
+      <c r="D537">
+        <v>1</v>
+      </c>
+      <c r="E537">
+        <f t="shared" si="55"/>
+        <v>4300</v>
+      </c>
+      <c r="F537">
+        <v>0.2</v>
+      </c>
+      <c r="G537">
+        <v>5</v>
+      </c>
+      <c r="H537">
+        <v>1</v>
+      </c>
+      <c r="I537">
+        <f t="shared" si="56"/>
+        <v>10000</v>
+      </c>
+      <c r="L537">
+        <v>2</v>
+      </c>
+      <c r="M537">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13">
+      <c r="A538" t="s">
+        <v>41</v>
+      </c>
+      <c r="B538" t="s">
+        <v>43</v>
+      </c>
+      <c r="C538">
+        <f t="shared" si="54"/>
+        <v>32</v>
+      </c>
+      <c r="D538">
+        <v>1</v>
+      </c>
+      <c r="E538">
+        <f t="shared" si="55"/>
+        <v>5000</v>
+      </c>
+      <c r="F538">
+        <v>0.2</v>
+      </c>
+      <c r="G538">
+        <v>5</v>
+      </c>
+      <c r="H538">
+        <v>1</v>
+      </c>
+      <c r="I538">
+        <f t="shared" si="56"/>
+        <v>12000</v>
+      </c>
+      <c r="L538">
+        <v>2</v>
+      </c>
+      <c r="M538">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13">
+      <c r="A539" t="s">
+        <v>41</v>
+      </c>
+      <c r="B539" t="s">
+        <v>43</v>
+      </c>
+      <c r="C539">
+        <f t="shared" si="54"/>
+        <v>33</v>
+      </c>
+      <c r="D539">
+        <v>1</v>
+      </c>
+      <c r="E539">
+        <f t="shared" si="55"/>
+        <v>6000</v>
+      </c>
+      <c r="F539">
+        <v>0.2</v>
+      </c>
+      <c r="G539">
+        <v>5</v>
+      </c>
+      <c r="H539">
+        <v>1</v>
+      </c>
+      <c r="I539">
+        <f t="shared" si="56"/>
+        <v>14500</v>
+      </c>
+      <c r="L539">
+        <v>2</v>
+      </c>
+      <c r="M539">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13">
+      <c r="A540" t="s">
+        <v>41</v>
+      </c>
+      <c r="B540" t="s">
+        <v>43</v>
+      </c>
+      <c r="C540">
+        <f t="shared" si="54"/>
+        <v>34</v>
+      </c>
+      <c r="D540">
+        <v>1</v>
+      </c>
+      <c r="E540">
+        <f t="shared" si="55"/>
+        <v>7000</v>
+      </c>
+      <c r="F540">
+        <v>0.2</v>
+      </c>
+      <c r="G540">
+        <v>5</v>
+      </c>
+      <c r="H540">
+        <v>1</v>
+      </c>
+      <c r="I540">
+        <f t="shared" si="56"/>
+        <v>17500</v>
+      </c>
+      <c r="L540">
+        <v>2</v>
+      </c>
+      <c r="M540">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13">
+      <c r="A541" t="s">
+        <v>41</v>
+      </c>
+      <c r="B541" t="s">
+        <v>43</v>
+      </c>
+      <c r="C541">
+        <f t="shared" si="54"/>
+        <v>35</v>
+      </c>
+      <c r="D541">
+        <v>1</v>
+      </c>
+      <c r="E541">
+        <f t="shared" si="55"/>
+        <v>8500</v>
+      </c>
+      <c r="F541">
+        <v>0.2</v>
+      </c>
+      <c r="G541">
+        <v>5</v>
+      </c>
+      <c r="H541">
+        <v>1</v>
+      </c>
+      <c r="I541">
+        <f t="shared" si="56"/>
+        <v>21000</v>
+      </c>
+      <c r="L541">
+        <v>2</v>
+      </c>
+      <c r="M541">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13">
+      <c r="A542" t="s">
+        <v>41</v>
+      </c>
+      <c r="B542" t="s">
+        <v>43</v>
+      </c>
+      <c r="C542">
+        <f t="shared" si="54"/>
+        <v>36</v>
+      </c>
+      <c r="D542">
+        <v>1</v>
+      </c>
+      <c r="E542">
+        <f t="shared" si="55"/>
+        <v>10000</v>
+      </c>
+      <c r="F542">
+        <v>0.2</v>
+      </c>
+      <c r="G542">
+        <v>5</v>
+      </c>
+      <c r="H542">
+        <v>1</v>
+      </c>
+      <c r="I542">
+        <f t="shared" si="56"/>
+        <v>25000</v>
+      </c>
+      <c r="L542">
+        <v>2</v>
+      </c>
+      <c r="M542">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13">
+      <c r="A543" t="s">
+        <v>41</v>
+      </c>
+      <c r="B543" t="s">
+        <v>43</v>
+      </c>
+      <c r="C543">
+        <f t="shared" si="54"/>
+        <v>37</v>
+      </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
+      <c r="E543">
+        <f t="shared" si="55"/>
+        <v>12000</v>
+      </c>
+      <c r="F543">
+        <v>0.2</v>
+      </c>
+      <c r="G543">
+        <v>5</v>
+      </c>
+      <c r="H543">
+        <v>1</v>
+      </c>
+      <c r="I543">
+        <f t="shared" si="56"/>
+        <v>30000</v>
+      </c>
+      <c r="L543">
+        <v>2</v>
+      </c>
+      <c r="M543">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13">
+      <c r="A544" t="s">
+        <v>41</v>
+      </c>
+      <c r="B544" t="s">
+        <v>43</v>
+      </c>
+      <c r="C544">
+        <f t="shared" si="54"/>
+        <v>38</v>
+      </c>
+      <c r="D544">
+        <v>1</v>
+      </c>
+      <c r="E544">
+        <f t="shared" si="55"/>
+        <v>14500</v>
+      </c>
+      <c r="F544">
+        <v>0.2</v>
+      </c>
+      <c r="G544">
+        <v>5</v>
+      </c>
+      <c r="H544">
+        <v>1</v>
+      </c>
+      <c r="I544">
+        <f t="shared" si="56"/>
+        <v>36000</v>
+      </c>
+      <c r="L544">
+        <v>2</v>
+      </c>
+      <c r="M544">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13">
+      <c r="A545" t="s">
+        <v>41</v>
+      </c>
+      <c r="B545" t="s">
+        <v>43</v>
+      </c>
+      <c r="C545">
+        <f t="shared" si="54"/>
+        <v>39</v>
+      </c>
+      <c r="D545">
+        <v>1</v>
+      </c>
+      <c r="E545">
+        <f t="shared" si="55"/>
+        <v>17500</v>
+      </c>
+      <c r="F545">
+        <v>0.2</v>
+      </c>
+      <c r="G545">
+        <v>5</v>
+      </c>
+      <c r="H545">
+        <v>1</v>
+      </c>
+      <c r="I545">
+        <f t="shared" si="56"/>
+        <v>43000</v>
+      </c>
+      <c r="L545">
+        <v>2</v>
+      </c>
+      <c r="M545">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13">
+      <c r="A546" t="s">
+        <v>41</v>
+      </c>
+      <c r="B546" t="s">
+        <v>43</v>
+      </c>
+      <c r="C546">
+        <f t="shared" si="54"/>
+        <v>40</v>
+      </c>
+      <c r="D546">
+        <v>1</v>
+      </c>
+      <c r="E546">
+        <f t="shared" si="55"/>
+        <v>21000</v>
+      </c>
+      <c r="F546">
+        <v>0.2</v>
+      </c>
+      <c r="G546">
+        <v>5</v>
+      </c>
+      <c r="H546">
+        <v>1</v>
+      </c>
+      <c r="I546">
+        <f t="shared" si="56"/>
+        <v>50000</v>
+      </c>
+      <c r="L546">
+        <v>2</v>
+      </c>
+      <c r="M546">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13">
+      <c r="A547" t="s">
+        <v>41</v>
+      </c>
+      <c r="B547" t="s">
+        <v>43</v>
+      </c>
+      <c r="C547">
+        <f t="shared" si="54"/>
+        <v>41</v>
+      </c>
+      <c r="D547">
+        <v>1</v>
+      </c>
+      <c r="E547">
+        <f t="shared" si="55"/>
+        <v>25000</v>
+      </c>
+      <c r="F547">
+        <v>0.2</v>
+      </c>
+      <c r="G547">
+        <v>5</v>
+      </c>
+      <c r="H547">
+        <v>1</v>
+      </c>
+      <c r="I547">
+        <f t="shared" si="56"/>
+        <v>60000</v>
+      </c>
+      <c r="L547">
+        <v>2</v>
+      </c>
+      <c r="M547">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13">
+      <c r="A548" t="s">
+        <v>41</v>
+      </c>
+      <c r="B548" t="s">
+        <v>43</v>
+      </c>
+      <c r="C548">
+        <f t="shared" si="54"/>
+        <v>42</v>
+      </c>
+      <c r="D548">
+        <v>1</v>
+      </c>
+      <c r="E548">
+        <f t="shared" si="55"/>
+        <v>30000</v>
+      </c>
+      <c r="F548">
+        <v>0.2</v>
+      </c>
+      <c r="G548">
+        <v>5</v>
+      </c>
+      <c r="H548">
+        <v>1</v>
+      </c>
+      <c r="I548">
+        <f t="shared" si="56"/>
+        <v>70000</v>
+      </c>
+      <c r="L548">
+        <v>2</v>
+      </c>
+      <c r="M548">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13">
+      <c r="A549" t="s">
+        <v>41</v>
+      </c>
+      <c r="B549" t="s">
+        <v>43</v>
+      </c>
+      <c r="C549">
+        <f t="shared" si="54"/>
+        <v>43</v>
+      </c>
+      <c r="D549">
+        <v>1</v>
+      </c>
+      <c r="E549">
+        <f t="shared" si="55"/>
+        <v>36000</v>
+      </c>
+      <c r="F549">
+        <v>0.2</v>
+      </c>
+      <c r="G549">
+        <v>5</v>
+      </c>
+      <c r="H549">
+        <v>1</v>
+      </c>
+      <c r="I549">
+        <f t="shared" si="56"/>
+        <v>85000</v>
+      </c>
+      <c r="L549">
+        <v>2</v>
+      </c>
+      <c r="M549">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13">
+      <c r="A550" t="s">
+        <v>41</v>
+      </c>
+      <c r="B550" t="s">
+        <v>43</v>
+      </c>
+      <c r="C550">
+        <f t="shared" si="54"/>
+        <v>44</v>
+      </c>
+      <c r="D550">
+        <v>1</v>
+      </c>
+      <c r="E550">
+        <f t="shared" si="55"/>
+        <v>43000</v>
+      </c>
+      <c r="F550">
+        <v>0.2</v>
+      </c>
+      <c r="G550">
+        <v>5</v>
+      </c>
+      <c r="H550">
+        <v>1</v>
+      </c>
+      <c r="I550">
+        <f t="shared" si="56"/>
+        <v>100000</v>
+      </c>
+      <c r="L550">
+        <v>2</v>
+      </c>
+      <c r="M550">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13">
+      <c r="A551" t="s">
+        <v>41</v>
+      </c>
+      <c r="B551" t="s">
+        <v>43</v>
+      </c>
+      <c r="C551">
+        <f t="shared" si="54"/>
+        <v>45</v>
+      </c>
+      <c r="D551">
+        <v>1</v>
+      </c>
+      <c r="E551">
+        <f t="shared" si="55"/>
+        <v>50000</v>
+      </c>
+      <c r="F551">
+        <v>0.2</v>
+      </c>
+      <c r="G551">
+        <v>5</v>
+      </c>
+      <c r="H551">
+        <v>1</v>
+      </c>
+      <c r="I551">
+        <f t="shared" si="56"/>
+        <v>120000</v>
+      </c>
+      <c r="L551">
+        <v>2</v>
+      </c>
+      <c r="M551">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13">
+      <c r="A552" t="s">
+        <v>41</v>
+      </c>
+      <c r="B552" t="s">
+        <v>43</v>
+      </c>
+      <c r="C552">
+        <f t="shared" si="54"/>
+        <v>46</v>
+      </c>
+      <c r="D552">
+        <v>1</v>
+      </c>
+      <c r="E552">
+        <f t="shared" si="55"/>
+        <v>60000</v>
+      </c>
+      <c r="F552">
+        <v>0.2</v>
+      </c>
+      <c r="G552">
+        <v>5</v>
+      </c>
+      <c r="H552">
+        <v>1</v>
+      </c>
+      <c r="I552">
+        <f t="shared" si="56"/>
+        <v>145000</v>
+      </c>
+      <c r="L552">
+        <v>2</v>
+      </c>
+      <c r="M552">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13">
+      <c r="A553" t="s">
+        <v>41</v>
+      </c>
+      <c r="B553" t="s">
+        <v>43</v>
+      </c>
+      <c r="C553">
+        <f t="shared" si="54"/>
+        <v>47</v>
+      </c>
+      <c r="D553">
+        <v>1</v>
+      </c>
+      <c r="E553">
+        <f t="shared" si="55"/>
+        <v>70000</v>
+      </c>
+      <c r="F553">
+        <v>0.2</v>
+      </c>
+      <c r="G553">
+        <v>5</v>
+      </c>
+      <c r="H553">
+        <v>1</v>
+      </c>
+      <c r="I553">
+        <f t="shared" si="56"/>
+        <v>175000</v>
+      </c>
+      <c r="L553">
+        <v>2</v>
+      </c>
+      <c r="M553">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13">
+      <c r="A554" t="s">
+        <v>41</v>
+      </c>
+      <c r="B554" t="s">
+        <v>43</v>
+      </c>
+      <c r="C554">
+        <f t="shared" si="54"/>
+        <v>48</v>
+      </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
+      <c r="E554">
+        <f t="shared" si="55"/>
+        <v>85000</v>
+      </c>
+      <c r="F554">
+        <v>0.2</v>
+      </c>
+      <c r="G554">
+        <v>5</v>
+      </c>
+      <c r="H554">
+        <v>1</v>
+      </c>
+      <c r="I554">
+        <f t="shared" si="56"/>
+        <v>210000</v>
+      </c>
+      <c r="L554">
+        <v>2</v>
+      </c>
+      <c r="M554">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13">
+      <c r="A555" t="s">
+        <v>41</v>
+      </c>
+      <c r="B555" t="s">
+        <v>43</v>
+      </c>
+      <c r="C555">
+        <f t="shared" si="54"/>
+        <v>49</v>
+      </c>
+      <c r="D555">
+        <v>1</v>
+      </c>
+      <c r="E555">
+        <f t="shared" si="55"/>
+        <v>100000</v>
+      </c>
+      <c r="F555">
+        <v>0.2</v>
+      </c>
+      <c r="G555">
+        <v>5</v>
+      </c>
+      <c r="H555">
+        <v>1</v>
+      </c>
+      <c r="I555">
+        <f t="shared" si="56"/>
+        <v>250000</v>
+      </c>
+      <c r="L555">
+        <v>2</v>
+      </c>
+      <c r="M555">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13">
+      <c r="A556" t="s">
+        <v>41</v>
+      </c>
+      <c r="B556" t="s">
+        <v>43</v>
+      </c>
+      <c r="C556">
+        <f t="shared" si="54"/>
+        <v>50</v>
+      </c>
+      <c r="D556">
+        <v>1</v>
+      </c>
+      <c r="E556">
+        <f t="shared" si="55"/>
+        <v>120000</v>
+      </c>
+      <c r="F556">
+        <v>0.2</v>
+      </c>
+      <c r="G556">
+        <v>5</v>
+      </c>
+      <c r="H556">
+        <v>1</v>
+      </c>
+      <c r="I556">
+        <f t="shared" si="56"/>
+        <v>300000</v>
+      </c>
+      <c r="L556">
+        <v>2</v>
+      </c>
+      <c r="M556">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13">
+      <c r="A557" t="s">
+        <v>41</v>
+      </c>
+      <c r="B557" t="s">
+        <v>43</v>
+      </c>
+      <c r="C557">
+        <f t="shared" si="54"/>
+        <v>51</v>
+      </c>
+      <c r="D557">
+        <v>1</v>
+      </c>
+      <c r="E557">
+        <f t="shared" si="55"/>
+        <v>145000</v>
+      </c>
+      <c r="F557">
+        <v>0.2</v>
+      </c>
+      <c r="G557">
+        <v>5</v>
+      </c>
+      <c r="H557">
+        <v>1</v>
+      </c>
+      <c r="I557">
+        <f t="shared" si="56"/>
+        <v>360000</v>
+      </c>
+      <c r="L557">
+        <v>2</v>
+      </c>
+      <c r="M557">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13">
+      <c r="A558" t="s">
+        <v>41</v>
+      </c>
+      <c r="B558" t="s">
+        <v>43</v>
+      </c>
+      <c r="C558">
+        <f t="shared" si="54"/>
+        <v>52</v>
+      </c>
+      <c r="D558">
+        <v>1</v>
+      </c>
+      <c r="E558">
+        <f t="shared" si="55"/>
+        <v>175000</v>
+      </c>
+      <c r="F558">
+        <v>0.2</v>
+      </c>
+      <c r="G558">
+        <v>5</v>
+      </c>
+      <c r="H558">
+        <v>1</v>
+      </c>
+      <c r="I558">
+        <f t="shared" si="56"/>
+        <v>430000</v>
+      </c>
+      <c r="L558">
+        <v>2</v>
+      </c>
+      <c r="M558">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13">
+      <c r="A559" t="s">
+        <v>41</v>
+      </c>
+      <c r="B559" t="s">
+        <v>43</v>
+      </c>
+      <c r="C559">
+        <f t="shared" si="54"/>
+        <v>53</v>
+      </c>
+      <c r="D559">
+        <v>1</v>
+      </c>
+      <c r="E559">
+        <f t="shared" si="55"/>
+        <v>210000</v>
+      </c>
+      <c r="F559">
+        <v>0.2</v>
+      </c>
+      <c r="G559">
+        <v>5</v>
+      </c>
+      <c r="H559">
+        <v>1</v>
+      </c>
+      <c r="I559">
+        <f t="shared" si="56"/>
+        <v>500000</v>
+      </c>
+      <c r="L559">
+        <v>2</v>
+      </c>
+      <c r="M559">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13">
+      <c r="A560" t="s">
+        <v>41</v>
+      </c>
+      <c r="B560" t="s">
+        <v>43</v>
+      </c>
+      <c r="C560">
+        <f t="shared" si="54"/>
+        <v>54</v>
+      </c>
+      <c r="D560">
+        <v>1</v>
+      </c>
+      <c r="E560">
+        <f t="shared" si="55"/>
+        <v>250000</v>
+      </c>
+      <c r="F560">
+        <v>0.2</v>
+      </c>
+      <c r="G560">
+        <v>5</v>
+      </c>
+      <c r="H560">
+        <v>1</v>
+      </c>
+      <c r="I560">
+        <f t="shared" si="56"/>
+        <v>600000</v>
+      </c>
+      <c r="L560">
+        <v>2</v>
+      </c>
+      <c r="M560">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13">
+      <c r="A561" t="s">
+        <v>41</v>
+      </c>
+      <c r="B561" t="s">
+        <v>43</v>
+      </c>
+      <c r="C561">
+        <f t="shared" si="54"/>
+        <v>55</v>
+      </c>
+      <c r="D561">
+        <v>1</v>
+      </c>
+      <c r="E561">
+        <f t="shared" si="55"/>
+        <v>300000</v>
+      </c>
+      <c r="F561">
+        <v>0.2</v>
+      </c>
+      <c r="G561">
+        <v>5</v>
+      </c>
+      <c r="H561">
+        <v>1</v>
+      </c>
+      <c r="I561">
+        <f t="shared" si="56"/>
+        <v>700000</v>
+      </c>
+      <c r="L561">
+        <v>2</v>
+      </c>
+      <c r="M561">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13">
+      <c r="A562" t="s">
+        <v>41</v>
+      </c>
+      <c r="B562" t="s">
+        <v>43</v>
+      </c>
+      <c r="C562">
+        <f t="shared" si="54"/>
+        <v>56</v>
+      </c>
+      <c r="D562">
+        <v>1</v>
+      </c>
+      <c r="E562">
+        <f t="shared" si="55"/>
+        <v>360000</v>
+      </c>
+      <c r="F562">
+        <v>0.2</v>
+      </c>
+      <c r="G562">
+        <v>5</v>
+      </c>
+      <c r="H562">
+        <v>1</v>
+      </c>
+      <c r="I562">
+        <f t="shared" si="56"/>
+        <v>850000</v>
+      </c>
+      <c r="L562">
+        <v>2</v>
+      </c>
+      <c r="M562">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13">
+      <c r="A563" t="s">
+        <v>41</v>
+      </c>
+      <c r="B563" t="s">
+        <v>43</v>
+      </c>
+      <c r="C563">
+        <f t="shared" si="54"/>
+        <v>57</v>
+      </c>
+      <c r="D563">
+        <v>1</v>
+      </c>
+      <c r="E563">
+        <f t="shared" si="55"/>
+        <v>430000</v>
+      </c>
+      <c r="F563">
+        <v>0.2</v>
+      </c>
+      <c r="G563">
+        <v>5</v>
+      </c>
+      <c r="H563">
+        <v>1</v>
+      </c>
+      <c r="I563">
+        <f t="shared" si="56"/>
+        <v>1000000</v>
+      </c>
+      <c r="L563">
+        <v>2</v>
+      </c>
+      <c r="M563">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13">
+      <c r="A564" t="s">
+        <v>41</v>
+      </c>
+      <c r="B564" t="s">
+        <v>43</v>
+      </c>
+      <c r="C564">
+        <f t="shared" si="54"/>
+        <v>58</v>
+      </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
+      <c r="E564">
+        <f t="shared" si="55"/>
+        <v>500000</v>
+      </c>
+      <c r="F564">
+        <v>0.2</v>
+      </c>
+      <c r="G564">
+        <v>5</v>
+      </c>
+      <c r="H564">
+        <v>1</v>
+      </c>
+      <c r="I564">
+        <f t="shared" si="56"/>
+        <v>1200000</v>
+      </c>
+      <c r="L564">
+        <v>2</v>
+      </c>
+      <c r="M564">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13">
+      <c r="A565" t="s">
+        <v>41</v>
+      </c>
+      <c r="B565" t="s">
+        <v>43</v>
+      </c>
+      <c r="C565">
+        <f t="shared" si="54"/>
+        <v>59</v>
+      </c>
+      <c r="D565">
+        <v>1</v>
+      </c>
+      <c r="E565">
+        <f t="shared" si="55"/>
+        <v>600000</v>
+      </c>
+      <c r="F565">
+        <v>0.2</v>
+      </c>
+      <c r="G565">
+        <v>5</v>
+      </c>
+      <c r="H565">
+        <v>1</v>
+      </c>
+      <c r="I565">
+        <f t="shared" si="56"/>
+        <v>1450000</v>
+      </c>
+      <c r="L565">
+        <v>2</v>
+      </c>
+      <c r="M565">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13">
+      <c r="A566" t="s">
+        <v>41</v>
+      </c>
+      <c r="B566" t="s">
+        <v>43</v>
+      </c>
+      <c r="C566">
+        <f t="shared" si="54"/>
+        <v>60</v>
+      </c>
+      <c r="D566">
+        <v>1</v>
+      </c>
+      <c r="E566">
+        <f t="shared" si="55"/>
+        <v>700000</v>
+      </c>
+      <c r="F566">
+        <v>0.2</v>
+      </c>
+      <c r="G566">
+        <v>5</v>
+      </c>
+      <c r="H566">
+        <v>1</v>
+      </c>
+      <c r="I566">
+        <f t="shared" si="56"/>
+        <v>1750000</v>
+      </c>
+      <c r="L566">
+        <v>2</v>
+      </c>
+      <c r="M566">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13">
+      <c r="A567" t="s">
+        <v>41</v>
+      </c>
+      <c r="B567" t="s">
+        <v>43</v>
+      </c>
+      <c r="C567">
+        <f t="shared" si="54"/>
+        <v>61</v>
+      </c>
+      <c r="D567">
+        <v>1</v>
+      </c>
+      <c r="E567">
+        <f t="shared" si="55"/>
+        <v>850000</v>
+      </c>
+      <c r="F567">
+        <v>0.2</v>
+      </c>
+      <c r="G567">
+        <v>5</v>
+      </c>
+      <c r="H567">
+        <v>1</v>
+      </c>
+      <c r="I567">
+        <f t="shared" si="56"/>
+        <v>2100000</v>
+      </c>
+      <c r="L567">
+        <v>2</v>
+      </c>
+      <c r="M567">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13">
+      <c r="A568" t="s">
+        <v>41</v>
+      </c>
+      <c r="B568" t="s">
+        <v>43</v>
+      </c>
+      <c r="C568">
+        <f t="shared" si="54"/>
+        <v>62</v>
+      </c>
+      <c r="D568">
+        <v>1</v>
+      </c>
+      <c r="E568">
+        <f t="shared" si="55"/>
+        <v>1000000</v>
+      </c>
+      <c r="F568">
+        <v>0.2</v>
+      </c>
+      <c r="G568">
+        <v>5</v>
+      </c>
+      <c r="H568">
+        <v>1</v>
+      </c>
+      <c r="I568">
+        <f t="shared" si="56"/>
+        <v>2500000</v>
+      </c>
+      <c r="L568">
+        <v>2</v>
+      </c>
+      <c r="M568">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13">
+      <c r="A569" t="s">
+        <v>41</v>
+      </c>
+      <c r="B569" t="s">
+        <v>43</v>
+      </c>
+      <c r="C569">
+        <f t="shared" si="54"/>
+        <v>63</v>
+      </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
+      <c r="E569">
+        <f t="shared" si="55"/>
+        <v>1200000</v>
+      </c>
+      <c r="F569">
+        <v>0.2</v>
+      </c>
+      <c r="G569">
+        <v>5</v>
+      </c>
+      <c r="H569">
+        <v>1</v>
+      </c>
+      <c r="I569">
+        <f t="shared" si="56"/>
+        <v>3000000</v>
+      </c>
+      <c r="L569">
+        <v>2</v>
+      </c>
+      <c r="M569">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13">
+      <c r="A570" t="s">
+        <v>41</v>
+      </c>
+      <c r="B570" t="s">
+        <v>43</v>
+      </c>
+      <c r="C570">
+        <f t="shared" si="54"/>
+        <v>64</v>
+      </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
+      <c r="E570">
+        <f t="shared" si="55"/>
+        <v>1450000</v>
+      </c>
+      <c r="F570">
+        <v>0.2</v>
+      </c>
+      <c r="G570">
+        <v>5</v>
+      </c>
+      <c r="H570">
+        <v>1</v>
+      </c>
+      <c r="I570">
+        <f t="shared" si="56"/>
+        <v>3600000</v>
+      </c>
+      <c r="L570">
+        <v>2</v>
+      </c>
+      <c r="M570">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13">
+      <c r="A571" t="s">
+        <v>41</v>
+      </c>
+      <c r="B571" t="s">
+        <v>43</v>
+      </c>
+      <c r="C571">
+        <f t="shared" si="54"/>
+        <v>65</v>
+      </c>
+      <c r="D571">
+        <v>1</v>
+      </c>
+      <c r="E571">
+        <f t="shared" si="55"/>
+        <v>1750000</v>
+      </c>
+      <c r="F571">
+        <v>0.2</v>
+      </c>
+      <c r="G571">
+        <v>5</v>
+      </c>
+      <c r="H571">
+        <v>1</v>
+      </c>
+      <c r="I571">
+        <f t="shared" si="56"/>
+        <v>4300000</v>
+      </c>
+      <c r="L571">
+        <v>2</v>
+      </c>
+      <c r="M571">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13">
+      <c r="A572" t="s">
+        <v>41</v>
+      </c>
+      <c r="B572" t="s">
+        <v>43</v>
+      </c>
+      <c r="C572">
+        <f t="shared" ref="C572:C606" si="57">C571+1</f>
+        <v>66</v>
+      </c>
+      <c r="D572">
+        <v>1</v>
+      </c>
+      <c r="E572">
+        <f t="shared" ref="E572:E606" si="58">ROUND(E571*1.2/5,IF(-(LEN(INT(ABS(E571*1.2/5)))-2)&lt;0,-(LEN(INT(ABS(E571*1.2/5)))-2),0))*5</f>
+        <v>2100000</v>
+      </c>
+      <c r="F572">
+        <v>0.2</v>
+      </c>
+      <c r="G572">
+        <v>5</v>
+      </c>
+      <c r="H572">
+        <v>1</v>
+      </c>
+      <c r="I572">
+        <f t="shared" ref="I572:I606" si="59">ROUND(I571*1.2/5,IF(-(LEN(INT(ABS(I571*1.2/5)))-2)&lt;0,-(LEN(INT(ABS(I571*1.2/5)))-2),0))*5</f>
+        <v>5000000</v>
+      </c>
+      <c r="L572">
+        <v>2</v>
+      </c>
+      <c r="M572">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13">
+      <c r="A573" t="s">
+        <v>41</v>
+      </c>
+      <c r="B573" t="s">
+        <v>43</v>
+      </c>
+      <c r="C573">
+        <f t="shared" si="57"/>
+        <v>67</v>
+      </c>
+      <c r="D573">
+        <v>1</v>
+      </c>
+      <c r="E573">
+        <f t="shared" si="58"/>
+        <v>2500000</v>
+      </c>
+      <c r="F573">
+        <v>0.2</v>
+      </c>
+      <c r="G573">
+        <v>5</v>
+      </c>
+      <c r="H573">
+        <v>1</v>
+      </c>
+      <c r="I573">
+        <f t="shared" si="59"/>
+        <v>6000000</v>
+      </c>
+      <c r="L573">
+        <v>2</v>
+      </c>
+      <c r="M573">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13">
+      <c r="A574" t="s">
+        <v>41</v>
+      </c>
+      <c r="B574" t="s">
+        <v>43</v>
+      </c>
+      <c r="C574">
+        <f t="shared" si="57"/>
+        <v>68</v>
+      </c>
+      <c r="D574">
+        <v>1</v>
+      </c>
+      <c r="E574">
+        <f t="shared" si="58"/>
+        <v>3000000</v>
+      </c>
+      <c r="F574">
+        <v>0.2</v>
+      </c>
+      <c r="G574">
+        <v>5</v>
+      </c>
+      <c r="H574">
+        <v>1</v>
+      </c>
+      <c r="I574">
+        <f t="shared" si="59"/>
+        <v>7000000</v>
+      </c>
+      <c r="L574">
+        <v>2</v>
+      </c>
+      <c r="M574">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13">
+      <c r="A575" t="s">
+        <v>41</v>
+      </c>
+      <c r="B575" t="s">
+        <v>43</v>
+      </c>
+      <c r="C575">
+        <f t="shared" si="57"/>
+        <v>69</v>
+      </c>
+      <c r="D575">
+        <v>1</v>
+      </c>
+      <c r="E575">
+        <f t="shared" si="58"/>
+        <v>3600000</v>
+      </c>
+      <c r="F575">
+        <v>0.2</v>
+      </c>
+      <c r="G575">
+        <v>5</v>
+      </c>
+      <c r="H575">
+        <v>1</v>
+      </c>
+      <c r="I575">
+        <f t="shared" si="59"/>
+        <v>8500000</v>
+      </c>
+      <c r="L575">
+        <v>2</v>
+      </c>
+      <c r="M575">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13">
+      <c r="A576" t="s">
+        <v>41</v>
+      </c>
+      <c r="B576" t="s">
+        <v>43</v>
+      </c>
+      <c r="C576">
+        <f t="shared" si="57"/>
+        <v>70</v>
+      </c>
+      <c r="D576">
+        <v>1</v>
+      </c>
+      <c r="E576">
+        <f t="shared" si="58"/>
+        <v>4300000</v>
+      </c>
+      <c r="F576">
+        <v>0.2</v>
+      </c>
+      <c r="G576">
+        <v>5</v>
+      </c>
+      <c r="H576">
+        <v>1</v>
+      </c>
+      <c r="I576">
+        <f t="shared" si="59"/>
+        <v>10000000</v>
+      </c>
+      <c r="L576">
+        <v>2</v>
+      </c>
+      <c r="M576">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13">
+      <c r="A577" t="s">
+        <v>41</v>
+      </c>
+      <c r="B577" t="s">
+        <v>43</v>
+      </c>
+      <c r="C577">
+        <f t="shared" si="57"/>
+        <v>71</v>
+      </c>
+      <c r="D577">
+        <v>1</v>
+      </c>
+      <c r="E577">
+        <f t="shared" si="58"/>
+        <v>5000000</v>
+      </c>
+      <c r="F577">
+        <v>0.2</v>
+      </c>
+      <c r="G577">
+        <v>5</v>
+      </c>
+      <c r="H577">
+        <v>1</v>
+      </c>
+      <c r="I577">
+        <f t="shared" si="59"/>
+        <v>12000000</v>
+      </c>
+      <c r="L577">
+        <v>2</v>
+      </c>
+      <c r="M577">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13">
+      <c r="A578" t="s">
+        <v>41</v>
+      </c>
+      <c r="B578" t="s">
+        <v>43</v>
+      </c>
+      <c r="C578">
+        <f t="shared" si="57"/>
+        <v>72</v>
+      </c>
+      <c r="D578">
+        <v>1</v>
+      </c>
+      <c r="E578">
+        <f t="shared" si="58"/>
+        <v>6000000</v>
+      </c>
+      <c r="F578">
+        <v>0.2</v>
+      </c>
+      <c r="G578">
+        <v>5</v>
+      </c>
+      <c r="H578">
+        <v>1</v>
+      </c>
+      <c r="I578">
+        <f t="shared" si="59"/>
+        <v>14500000</v>
+      </c>
+      <c r="L578">
+        <v>2</v>
+      </c>
+      <c r="M578">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13">
+      <c r="A579" t="s">
+        <v>41</v>
+      </c>
+      <c r="B579" t="s">
+        <v>43</v>
+      </c>
+      <c r="C579">
+        <f t="shared" si="57"/>
+        <v>73</v>
+      </c>
+      <c r="D579">
+        <v>1</v>
+      </c>
+      <c r="E579">
+        <f t="shared" si="58"/>
+        <v>7000000</v>
+      </c>
+      <c r="F579">
+        <v>0.2</v>
+      </c>
+      <c r="G579">
+        <v>5</v>
+      </c>
+      <c r="H579">
+        <v>1</v>
+      </c>
+      <c r="I579">
+        <f t="shared" si="59"/>
+        <v>17500000</v>
+      </c>
+      <c r="L579">
+        <v>2</v>
+      </c>
+      <c r="M579">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13">
+      <c r="A580" t="s">
+        <v>41</v>
+      </c>
+      <c r="B580" t="s">
+        <v>43</v>
+      </c>
+      <c r="C580">
+        <f t="shared" si="57"/>
+        <v>74</v>
+      </c>
+      <c r="D580">
+        <v>1</v>
+      </c>
+      <c r="E580">
+        <f t="shared" si="58"/>
+        <v>8500000</v>
+      </c>
+      <c r="F580">
+        <v>0.2</v>
+      </c>
+      <c r="G580">
+        <v>5</v>
+      </c>
+      <c r="H580">
+        <v>1</v>
+      </c>
+      <c r="I580">
+        <f t="shared" si="59"/>
+        <v>21000000</v>
+      </c>
+      <c r="L580">
+        <v>2</v>
+      </c>
+      <c r="M580">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13">
+      <c r="A581" t="s">
+        <v>41</v>
+      </c>
+      <c r="B581" t="s">
+        <v>43</v>
+      </c>
+      <c r="C581">
+        <f t="shared" si="57"/>
+        <v>75</v>
+      </c>
+      <c r="D581">
+        <v>1</v>
+      </c>
+      <c r="E581">
+        <f t="shared" si="58"/>
+        <v>10000000</v>
+      </c>
+      <c r="F581">
+        <v>0.2</v>
+      </c>
+      <c r="G581">
+        <v>5</v>
+      </c>
+      <c r="H581">
+        <v>1</v>
+      </c>
+      <c r="I581">
+        <f t="shared" si="59"/>
+        <v>25000000</v>
+      </c>
+      <c r="L581">
+        <v>2</v>
+      </c>
+      <c r="M581">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13">
+      <c r="A582" t="s">
+        <v>41</v>
+      </c>
+      <c r="B582" t="s">
+        <v>43</v>
+      </c>
+      <c r="C582">
+        <f t="shared" si="57"/>
+        <v>76</v>
+      </c>
+      <c r="D582">
+        <v>1</v>
+      </c>
+      <c r="E582">
+        <f t="shared" si="58"/>
+        <v>12000000</v>
+      </c>
+      <c r="F582">
+        <v>0.2</v>
+      </c>
+      <c r="G582">
+        <v>5</v>
+      </c>
+      <c r="H582">
+        <v>1</v>
+      </c>
+      <c r="I582">
+        <f t="shared" si="59"/>
+        <v>30000000</v>
+      </c>
+      <c r="L582">
+        <v>2</v>
+      </c>
+      <c r="M582">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13">
+      <c r="A583" t="s">
+        <v>41</v>
+      </c>
+      <c r="B583" t="s">
+        <v>43</v>
+      </c>
+      <c r="C583">
+        <f t="shared" si="57"/>
+        <v>77</v>
+      </c>
+      <c r="D583">
+        <v>1</v>
+      </c>
+      <c r="E583">
+        <f t="shared" si="58"/>
+        <v>14500000</v>
+      </c>
+      <c r="F583">
+        <v>0.2</v>
+      </c>
+      <c r="G583">
+        <v>5</v>
+      </c>
+      <c r="H583">
+        <v>1</v>
+      </c>
+      <c r="I583">
+        <f t="shared" si="59"/>
+        <v>36000000</v>
+      </c>
+      <c r="L583">
+        <v>2</v>
+      </c>
+      <c r="M583">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13">
+      <c r="A584" t="s">
+        <v>41</v>
+      </c>
+      <c r="B584" t="s">
+        <v>43</v>
+      </c>
+      <c r="C584">
+        <f t="shared" si="57"/>
+        <v>78</v>
+      </c>
+      <c r="D584">
+        <v>1</v>
+      </c>
+      <c r="E584">
+        <f t="shared" si="58"/>
+        <v>17500000</v>
+      </c>
+      <c r="F584">
+        <v>0.2</v>
+      </c>
+      <c r="G584">
+        <v>5</v>
+      </c>
+      <c r="H584">
+        <v>1</v>
+      </c>
+      <c r="I584">
+        <f t="shared" si="59"/>
+        <v>43000000</v>
+      </c>
+      <c r="L584">
+        <v>2</v>
+      </c>
+      <c r="M584">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13">
+      <c r="A585" t="s">
+        <v>41</v>
+      </c>
+      <c r="B585" t="s">
+        <v>43</v>
+      </c>
+      <c r="C585">
+        <f t="shared" si="57"/>
+        <v>79</v>
+      </c>
+      <c r="D585">
+        <v>1</v>
+      </c>
+      <c r="E585">
+        <f t="shared" si="58"/>
+        <v>21000000</v>
+      </c>
+      <c r="F585">
+        <v>0.2</v>
+      </c>
+      <c r="G585">
+        <v>5</v>
+      </c>
+      <c r="H585">
+        <v>1</v>
+      </c>
+      <c r="I585">
+        <f t="shared" si="59"/>
+        <v>50000000</v>
+      </c>
+      <c r="L585">
+        <v>2</v>
+      </c>
+      <c r="M585">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13">
+      <c r="A586" t="s">
+        <v>41</v>
+      </c>
+      <c r="B586" t="s">
+        <v>43</v>
+      </c>
+      <c r="C586">
+        <f t="shared" si="57"/>
+        <v>80</v>
+      </c>
+      <c r="D586">
+        <v>1</v>
+      </c>
+      <c r="E586">
+        <f t="shared" si="58"/>
+        <v>25000000</v>
+      </c>
+      <c r="F586">
+        <v>0.2</v>
+      </c>
+      <c r="G586">
+        <v>5</v>
+      </c>
+      <c r="H586">
+        <v>1</v>
+      </c>
+      <c r="I586">
+        <f t="shared" si="59"/>
+        <v>60000000</v>
+      </c>
+      <c r="L586">
+        <v>2</v>
+      </c>
+      <c r="M586">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13">
+      <c r="A587" t="s">
+        <v>41</v>
+      </c>
+      <c r="B587" t="s">
+        <v>43</v>
+      </c>
+      <c r="C587">
+        <f t="shared" si="57"/>
+        <v>81</v>
+      </c>
+      <c r="D587">
+        <v>1</v>
+      </c>
+      <c r="E587">
+        <f t="shared" si="58"/>
+        <v>30000000</v>
+      </c>
+      <c r="F587">
+        <v>0.2</v>
+      </c>
+      <c r="G587">
+        <v>5</v>
+      </c>
+      <c r="H587">
+        <v>1</v>
+      </c>
+      <c r="I587">
+        <f t="shared" si="59"/>
+        <v>70000000</v>
+      </c>
+      <c r="L587">
+        <v>2</v>
+      </c>
+      <c r="M587">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13">
+      <c r="A588" t="s">
+        <v>41</v>
+      </c>
+      <c r="B588" t="s">
+        <v>43</v>
+      </c>
+      <c r="C588">
+        <f t="shared" si="57"/>
+        <v>82</v>
+      </c>
+      <c r="D588">
+        <v>1</v>
+      </c>
+      <c r="E588">
+        <f t="shared" si="58"/>
+        <v>36000000</v>
+      </c>
+      <c r="F588">
+        <v>0.2</v>
+      </c>
+      <c r="G588">
+        <v>5</v>
+      </c>
+      <c r="H588">
+        <v>1</v>
+      </c>
+      <c r="I588">
+        <f t="shared" si="59"/>
+        <v>85000000</v>
+      </c>
+      <c r="L588">
+        <v>2</v>
+      </c>
+      <c r="M588">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13">
+      <c r="A589" t="s">
+        <v>41</v>
+      </c>
+      <c r="B589" t="s">
+        <v>43</v>
+      </c>
+      <c r="C589">
+        <f t="shared" si="57"/>
+        <v>83</v>
+      </c>
+      <c r="D589">
+        <v>1</v>
+      </c>
+      <c r="E589">
+        <f t="shared" si="58"/>
+        <v>43000000</v>
+      </c>
+      <c r="F589">
+        <v>0.2</v>
+      </c>
+      <c r="G589">
+        <v>5</v>
+      </c>
+      <c r="H589">
+        <v>1</v>
+      </c>
+      <c r="I589">
+        <f t="shared" si="59"/>
+        <v>100000000</v>
+      </c>
+      <c r="L589">
+        <v>2</v>
+      </c>
+      <c r="M589">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13">
+      <c r="A590" t="s">
+        <v>41</v>
+      </c>
+      <c r="B590" t="s">
+        <v>43</v>
+      </c>
+      <c r="C590">
+        <f t="shared" si="57"/>
+        <v>84</v>
+      </c>
+      <c r="D590">
+        <v>1</v>
+      </c>
+      <c r="E590">
+        <f t="shared" si="58"/>
+        <v>50000000</v>
+      </c>
+      <c r="F590">
+        <v>0.2</v>
+      </c>
+      <c r="G590">
+        <v>5</v>
+      </c>
+      <c r="H590">
+        <v>1</v>
+      </c>
+      <c r="I590">
+        <f t="shared" si="59"/>
+        <v>120000000</v>
+      </c>
+      <c r="L590">
+        <v>2</v>
+      </c>
+      <c r="M590">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13">
+      <c r="A591" t="s">
+        <v>41</v>
+      </c>
+      <c r="B591" t="s">
+        <v>43</v>
+      </c>
+      <c r="C591">
+        <f t="shared" si="57"/>
+        <v>85</v>
+      </c>
+      <c r="D591">
+        <v>1</v>
+      </c>
+      <c r="E591">
+        <f t="shared" si="58"/>
+        <v>60000000</v>
+      </c>
+      <c r="F591">
+        <v>0.2</v>
+      </c>
+      <c r="G591">
+        <v>5</v>
+      </c>
+      <c r="H591">
+        <v>1</v>
+      </c>
+      <c r="I591">
+        <f t="shared" si="59"/>
+        <v>145000000</v>
+      </c>
+      <c r="L591">
+        <v>2</v>
+      </c>
+      <c r="M591">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13">
+      <c r="A592" t="s">
+        <v>41</v>
+      </c>
+      <c r="B592" t="s">
+        <v>43</v>
+      </c>
+      <c r="C592">
+        <f t="shared" si="57"/>
+        <v>86</v>
+      </c>
+      <c r="D592">
+        <v>1</v>
+      </c>
+      <c r="E592">
+        <f t="shared" si="58"/>
+        <v>70000000</v>
+      </c>
+      <c r="F592">
+        <v>0.2</v>
+      </c>
+      <c r="G592">
+        <v>5</v>
+      </c>
+      <c r="H592">
+        <v>1</v>
+      </c>
+      <c r="I592">
+        <f t="shared" si="59"/>
+        <v>175000000</v>
+      </c>
+      <c r="L592">
+        <v>2</v>
+      </c>
+      <c r="M592">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13">
+      <c r="A593" t="s">
+        <v>41</v>
+      </c>
+      <c r="B593" t="s">
+        <v>43</v>
+      </c>
+      <c r="C593">
+        <f t="shared" si="57"/>
+        <v>87</v>
+      </c>
+      <c r="D593">
+        <v>1</v>
+      </c>
+      <c r="E593">
+        <f t="shared" si="58"/>
+        <v>85000000</v>
+      </c>
+      <c r="F593">
+        <v>0.2</v>
+      </c>
+      <c r="G593">
+        <v>5</v>
+      </c>
+      <c r="H593">
+        <v>1</v>
+      </c>
+      <c r="I593">
+        <f t="shared" si="59"/>
+        <v>210000000</v>
+      </c>
+      <c r="L593">
+        <v>2</v>
+      </c>
+      <c r="M593">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13">
+      <c r="A594" t="s">
+        <v>41</v>
+      </c>
+      <c r="B594" t="s">
+        <v>43</v>
+      </c>
+      <c r="C594">
+        <f t="shared" si="57"/>
+        <v>88</v>
+      </c>
+      <c r="D594">
+        <v>1</v>
+      </c>
+      <c r="E594">
+        <f t="shared" si="58"/>
+        <v>100000000</v>
+      </c>
+      <c r="F594">
+        <v>0.2</v>
+      </c>
+      <c r="G594">
+        <v>5</v>
+      </c>
+      <c r="H594">
+        <v>1</v>
+      </c>
+      <c r="I594">
+        <f t="shared" si="59"/>
+        <v>250000000</v>
+      </c>
+      <c r="L594">
+        <v>2</v>
+      </c>
+      <c r="M594">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13">
+      <c r="A595" t="s">
+        <v>41</v>
+      </c>
+      <c r="B595" t="s">
+        <v>43</v>
+      </c>
+      <c r="C595">
+        <f t="shared" si="57"/>
+        <v>89</v>
+      </c>
+      <c r="D595">
+        <v>1</v>
+      </c>
+      <c r="E595">
+        <f t="shared" si="58"/>
+        <v>120000000</v>
+      </c>
+      <c r="F595">
+        <v>0.2</v>
+      </c>
+      <c r="G595">
+        <v>5</v>
+      </c>
+      <c r="H595">
+        <v>1</v>
+      </c>
+      <c r="I595">
+        <f t="shared" si="59"/>
+        <v>300000000</v>
+      </c>
+      <c r="L595">
+        <v>2</v>
+      </c>
+      <c r="M595">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13">
+      <c r="A596" t="s">
+        <v>41</v>
+      </c>
+      <c r="B596" t="s">
+        <v>43</v>
+      </c>
+      <c r="C596">
+        <f t="shared" si="57"/>
+        <v>90</v>
+      </c>
+      <c r="D596">
+        <v>1</v>
+      </c>
+      <c r="E596">
+        <f t="shared" si="58"/>
+        <v>145000000</v>
+      </c>
+      <c r="F596">
+        <v>0.2</v>
+      </c>
+      <c r="G596">
+        <v>5</v>
+      </c>
+      <c r="H596">
+        <v>1</v>
+      </c>
+      <c r="I596">
+        <f t="shared" si="59"/>
+        <v>360000000</v>
+      </c>
+      <c r="L596">
+        <v>2</v>
+      </c>
+      <c r="M596">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13">
+      <c r="A597" t="s">
+        <v>41</v>
+      </c>
+      <c r="B597" t="s">
+        <v>43</v>
+      </c>
+      <c r="C597">
+        <f t="shared" si="57"/>
+        <v>91</v>
+      </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
+      <c r="E597">
+        <f t="shared" si="58"/>
+        <v>175000000</v>
+      </c>
+      <c r="F597">
+        <v>0.2</v>
+      </c>
+      <c r="G597">
+        <v>5</v>
+      </c>
+      <c r="H597">
+        <v>1</v>
+      </c>
+      <c r="I597">
+        <f t="shared" si="59"/>
+        <v>430000000</v>
+      </c>
+      <c r="L597">
+        <v>2</v>
+      </c>
+      <c r="M597">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13">
+      <c r="A598" t="s">
+        <v>41</v>
+      </c>
+      <c r="B598" t="s">
+        <v>43</v>
+      </c>
+      <c r="C598">
+        <f t="shared" si="57"/>
+        <v>92</v>
+      </c>
+      <c r="D598">
+        <v>1</v>
+      </c>
+      <c r="E598">
+        <f t="shared" si="58"/>
+        <v>210000000</v>
+      </c>
+      <c r="F598">
+        <v>0.2</v>
+      </c>
+      <c r="G598">
+        <v>5</v>
+      </c>
+      <c r="H598">
+        <v>1</v>
+      </c>
+      <c r="I598">
+        <f t="shared" si="59"/>
+        <v>500000000</v>
+      </c>
+      <c r="L598">
+        <v>2</v>
+      </c>
+      <c r="M598">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13">
+      <c r="A599" t="s">
+        <v>41</v>
+      </c>
+      <c r="B599" t="s">
+        <v>43</v>
+      </c>
+      <c r="C599">
+        <f t="shared" si="57"/>
+        <v>93</v>
+      </c>
+      <c r="D599">
+        <v>1</v>
+      </c>
+      <c r="E599">
+        <f t="shared" si="58"/>
+        <v>250000000</v>
+      </c>
+      <c r="F599">
+        <v>0.2</v>
+      </c>
+      <c r="G599">
+        <v>5</v>
+      </c>
+      <c r="H599">
+        <v>1</v>
+      </c>
+      <c r="I599">
+        <f t="shared" si="59"/>
+        <v>600000000</v>
+      </c>
+      <c r="L599">
+        <v>2</v>
+      </c>
+      <c r="M599">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13">
+      <c r="A600" t="s">
+        <v>41</v>
+      </c>
+      <c r="B600" t="s">
+        <v>43</v>
+      </c>
+      <c r="C600">
+        <f t="shared" si="57"/>
+        <v>94</v>
+      </c>
+      <c r="D600">
+        <v>1</v>
+      </c>
+      <c r="E600">
+        <f t="shared" si="58"/>
+        <v>300000000</v>
+      </c>
+      <c r="F600">
+        <v>0.2</v>
+      </c>
+      <c r="G600">
+        <v>5</v>
+      </c>
+      <c r="H600">
+        <v>1</v>
+      </c>
+      <c r="I600">
+        <f t="shared" si="59"/>
+        <v>700000000</v>
+      </c>
+      <c r="L600">
+        <v>2</v>
+      </c>
+      <c r="M600">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13">
+      <c r="A601" t="s">
+        <v>41</v>
+      </c>
+      <c r="B601" t="s">
+        <v>43</v>
+      </c>
+      <c r="C601">
+        <f t="shared" si="57"/>
+        <v>95</v>
+      </c>
+      <c r="D601">
+        <v>1</v>
+      </c>
+      <c r="E601">
+        <f t="shared" si="58"/>
+        <v>360000000</v>
+      </c>
+      <c r="F601">
+        <v>0.2</v>
+      </c>
+      <c r="G601">
+        <v>5</v>
+      </c>
+      <c r="H601">
+        <v>1</v>
+      </c>
+      <c r="I601">
+        <f t="shared" si="59"/>
+        <v>850000000</v>
+      </c>
+      <c r="L601">
+        <v>2</v>
+      </c>
+      <c r="M601">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13">
+      <c r="A602" t="s">
+        <v>41</v>
+      </c>
+      <c r="B602" t="s">
+        <v>43</v>
+      </c>
+      <c r="C602">
+        <f t="shared" si="57"/>
+        <v>96</v>
+      </c>
+      <c r="D602">
+        <v>1</v>
+      </c>
+      <c r="E602">
+        <f t="shared" si="58"/>
+        <v>430000000</v>
+      </c>
+      <c r="F602">
+        <v>0.2</v>
+      </c>
+      <c r="G602">
+        <v>5</v>
+      </c>
+      <c r="H602">
+        <v>1</v>
+      </c>
+      <c r="I602">
+        <f t="shared" si="59"/>
+        <v>1000000000</v>
+      </c>
+      <c r="L602">
+        <v>2</v>
+      </c>
+      <c r="M602">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13">
+      <c r="A603" t="s">
+        <v>41</v>
+      </c>
+      <c r="B603" t="s">
+        <v>43</v>
+      </c>
+      <c r="C603">
+        <f t="shared" si="57"/>
+        <v>97</v>
+      </c>
+      <c r="D603">
+        <v>1</v>
+      </c>
+      <c r="E603">
+        <f t="shared" si="58"/>
+        <v>500000000</v>
+      </c>
+      <c r="F603">
+        <v>0.2</v>
+      </c>
+      <c r="G603">
+        <v>5</v>
+      </c>
+      <c r="H603">
+        <v>1</v>
+      </c>
+      <c r="I603">
+        <f t="shared" si="59"/>
+        <v>1200000000</v>
+      </c>
+      <c r="L603">
+        <v>2</v>
+      </c>
+      <c r="M603">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13">
+      <c r="A604" t="s">
+        <v>41</v>
+      </c>
+      <c r="B604" t="s">
+        <v>43</v>
+      </c>
+      <c r="C604">
+        <f t="shared" si="57"/>
+        <v>98</v>
+      </c>
+      <c r="D604">
+        <v>1</v>
+      </c>
+      <c r="E604">
+        <f t="shared" si="58"/>
+        <v>600000000</v>
+      </c>
+      <c r="F604">
+        <v>0.2</v>
+      </c>
+      <c r="G604">
+        <v>5</v>
+      </c>
+      <c r="H604">
+        <v>1</v>
+      </c>
+      <c r="I604">
+        <f t="shared" si="59"/>
+        <v>1450000000</v>
+      </c>
+      <c r="L604">
+        <v>2</v>
+      </c>
+      <c r="M604">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13">
+      <c r="A605" t="s">
+        <v>41</v>
+      </c>
+      <c r="B605" t="s">
+        <v>43</v>
+      </c>
+      <c r="C605">
+        <f t="shared" si="57"/>
+        <v>99</v>
+      </c>
+      <c r="D605">
+        <v>1</v>
+      </c>
+      <c r="E605">
+        <f t="shared" si="58"/>
+        <v>700000000</v>
+      </c>
+      <c r="F605">
+        <v>0.2</v>
+      </c>
+      <c r="G605">
+        <v>5</v>
+      </c>
+      <c r="H605">
+        <v>1</v>
+      </c>
+      <c r="I605">
+        <f t="shared" si="59"/>
+        <v>1750000000</v>
+      </c>
+      <c r="L605">
+        <v>2</v>
+      </c>
+      <c r="M605">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13">
+      <c r="A606" t="s">
+        <v>41</v>
+      </c>
+      <c r="B606" t="s">
+        <v>43</v>
+      </c>
+      <c r="C606">
+        <f t="shared" si="57"/>
+        <v>100</v>
+      </c>
+      <c r="D606">
+        <v>1</v>
+      </c>
+      <c r="E606">
+        <f t="shared" si="58"/>
+        <v>850000000</v>
+      </c>
+      <c r="F606">
+        <v>0.2</v>
+      </c>
+      <c r="G606">
+        <v>5</v>
+      </c>
+      <c r="H606">
+        <v>1</v>
+      </c>
+      <c r="I606">
+        <f t="shared" si="59"/>
+        <v>2100000000</v>
+      </c>
+      <c r="L606">
+        <v>2</v>
+      </c>
+      <c r="M606">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1358,10 +1358,10 @@
         <v>500</v>
       </c>
       <c r="P5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>0.2</v>
@@ -1387,7 +1387,7 @@
         <v>0.2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1399,7 +1399,7 @@
         <v>0.2</v>
       </c>
       <c r="O6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1422,7 +1422,7 @@
         <v>0.2</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1440,7 +1440,7 @@
         <v>3</v>
       </c>
       <c r="P7">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1463,7 +1463,7 @@
         <v>0.2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1478,7 +1478,7 @@
         <v>0.2</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:18">
@@ -1495,10 +1495,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O9">
         <v>20</v>
@@ -1521,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <v>3</v>
@@ -1544,10 +1544,10 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>0.2</v>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>0.2</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
   <si>
     <t>name</t>
   </si>
@@ -50,9 +50,6 @@
     <t>cd</t>
   </si>
   <si>
-    <t>unlock</t>
-  </si>
-  <si>
     <t>res_1</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
   </si>
   <si>
     <t>武器发射需要的时间</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
   </si>
   <si>
     <t>升级该武器需要的资源</t>
@@ -1142,158 +1136,149 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1325,10 +1310,10 @@
     </row>
     <row r="5" customFormat="1" spans="1:18">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1341,9 +1326,6 @@
       </c>
       <c r="G5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1369,10 +1351,10 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1404,10 +1386,10 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1422,9 +1404,6 @@
         <v>0.2</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
@@ -1445,10 +1424,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1464,9 +1443,6 @@
       </c>
       <c r="G8">
         <v>1</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1483,10 +1459,10 @@
     </row>
     <row r="9" customFormat="1" spans="1:18">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1506,10 +1482,10 @@
     </row>
     <row r="10" customFormat="1" spans="1:18">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1532,10 +1508,10 @@
     </row>
     <row r="11" customFormat="1" spans="1:18">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1555,10 +1531,10 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1575,9 +1551,6 @@
       <c r="G12">
         <v>0.2</v>
       </c>
-      <c r="H12">
-        <v>5</v>
-      </c>
       <c r="I12">
         <v>1</v>
       </c>
@@ -1591,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1599,10 +1572,10 @@
     </row>
     <row r="13" customFormat="1" spans="1:18">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1618,9 +1591,6 @@
       </c>
       <c r="G13">
         <v>0.2</v>
-      </c>
-      <c r="H13">
-        <v>5</v>
       </c>
       <c r="I13">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="equipment" sheetId="3" r:id="rId1"/>
@@ -1105,13 +1110,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="4" max="6" width="9" customWidth="1"/>
-    <col min="10" max="14" width="10.225" customWidth="1"/>
-    <col min="15" max="15" width="12.625"/>
+    <col min="10" max="14" width="10.2222222222222" customWidth="1"/>
+    <col min="15" max="15" width="12.6296296296296"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1340,7 +1345,7 @@
         <v>500</v>
       </c>
       <c r="P5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -1398,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F7">
         <v>0.2</v>
@@ -1416,7 +1421,7 @@
         <v>0.2</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7">
         <v>20</v>
@@ -1543,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>0.2</v>
@@ -1584,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>0.2</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1454,7 +1454,7 @@
         <v>0.2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I8">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1584,7 +1584,7 @@
         <v>0.2</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
+          <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S；敌方能量攻击原模板，dmgtype=1；与物理攻击变体配对。</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
+          <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S；敌方物理攻击配对变体复用，dmgtype=2；防具响应取实际伤害类型，不改敌方防御。</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>35</v>
+        <v>62.5</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1413,13 +1413,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>200</v>
+        <v>208.5</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.2</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="0" t="n">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="equipment" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1374,13 +1374,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.2</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>30</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7">

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1413,7 +1413,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.2</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1380,7 +1380,7 @@
         <v>0.2</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.2</v>
@@ -1431,7 +1431,7 @@
         <v>0.2</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" s="0" t="n">
         <v>30</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1380,7 +1380,7 @@
         <v>0.2</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>1</v>
@@ -1431,7 +1431,7 @@
         <v>0.2</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" s="0" t="n">
         <v>30</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1373,8 +1373,8 @@
       <c r="D6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>300</v>
+      <c r="E6" s="0">
+        <v>350</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.2</v>
@@ -1412,8 +1412,8 @@
       <c r="D7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>200</v>
+      <c r="E7" s="0">
+        <v>170</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.2</v>
@@ -1454,8 +1454,8 @@
       <c r="D8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>1500</v>
+      <c r="E8" s="0">
+        <v>1200</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.2</v>
@@ -1583,8 +1583,8 @@
       <c r="F12" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>0.28</v>
+      <c r="G12" s="0">
+        <v>0.25</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>1</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1373,7 +1373,7 @@
       <c r="D6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="0" t="n">
         <v>350</v>
       </c>
       <c r="F6" s="0" t="n">
@@ -1392,7 +1392,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>10000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1412,7 +1412,7 @@
       <c r="D7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="0" t="n">
         <v>170</v>
       </c>
       <c r="F7" s="0" t="n">
@@ -1454,7 +1454,7 @@
       <c r="D8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="0" t="n">
         <v>1200</v>
       </c>
       <c r="F8" s="0" t="n">
@@ -1583,7 +1583,7 @@
       <c r="F12" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="0">
+      <c r="G12" s="0" t="n">
         <v>0.25</v>
       </c>
       <c r="I12" s="0" t="n">

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤,para4是para1随等级的增加值,算法为para1*(1+para4)^(等级-1),除了首2位其他位都是0,四舍五入,如果不足100,则末尾为5</t>
+          <t>飞船基础护盾，先于装甲承伤；dmgtype为其抗性类型。para1是1级容量；同等级容量取装甲按原规则取整后的数值，再乘para1/装甲para1，确保所有等级维持同一比例。para2为每秒恢复最大容量的比例，para3为每次受击后等待秒数；para4须与装甲成长率一致，供导入校验。</t>
         </is>
       </c>
       <c r="C5" s="0" t="n">
@@ -1344,7 +1344,7 @@
         <v>0.2</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="P5" s="0" t="n">
         <v>0.3</v>

--- a/space-battleship/config_excel/equipment.xlsx
+++ b/space-battleship/config_excel/equipment.xlsx
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="1"/>
@@ -1650,6 +1650,33 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>laser-mon</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>敌方低频单发能量激光；para1 为飞行速度，冷却用于留出玩家护盾恢复窗口。</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
